--- a/nongup_josagu/nongup_area_josagu.xlsx
+++ b/nongup_josagu/nongup_area_josagu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ubaldos/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ubaldos/Downloads/nongup_josagu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42DC2E24-035A-A84B-A825-B89C8E14FD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF60702-250E-1840-A410-FA62050C4ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11540" yWindow="5540" windowWidth="28100" windowHeight="17080" xr2:uid="{E426F48E-CE9B-944A-9245-D87549234143}"/>
+    <workbookView xWindow="14200" yWindow="3800" windowWidth="28100" windowHeight="17080" xr2:uid="{E426F48E-CE9B-944A-9245-D87549234143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,6 +94,14 @@
   </si>
   <si>
     <t>경상북도 경산시 자인면 북사리 359</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -189,6 +197,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -508,18 +520,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2D2C29-17FF-E146-AC0F-D15A7C12C019}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="7" max="7" width="36.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,10 +556,16 @@
         <v>6</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -567,9 +587,11 @@
       <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -579,9 +601,11 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -591,9 +615,11 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -603,9 +629,11 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -615,9 +643,11 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -627,9 +657,11 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -639,9 +671,11 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -651,9 +685,11 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -663,9 +699,11 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -675,9 +713,11 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -687,9 +727,11 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -699,9 +741,11 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -711,9 +755,11 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -723,9 +769,11 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -735,9 +783,11 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -747,9 +797,11 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -759,9 +811,11 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -771,9 +825,11 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -783,9 +839,11 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -795,9 +853,11 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -807,9 +867,11 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -819,9 +881,11 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -831,9 +895,11 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -843,9 +909,11 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -855,9 +923,11 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -867,9 +937,11 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -879,9 +951,11 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -891,9 +965,11 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -903,9 +979,11 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -915,9 +993,11 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -927,9 +1007,11 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1">
         <v>32</v>
       </c>
@@ -939,9 +1021,11 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="1">
         <v>33</v>
       </c>
@@ -951,9 +1035,11 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1">
         <v>34</v>
       </c>
@@ -963,9 +1049,11 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="1">
         <v>35</v>
       </c>
@@ -975,9 +1063,11 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1">
         <v>36</v>
       </c>
@@ -987,9 +1077,11 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>37</v>
       </c>
@@ -999,9 +1091,11 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="5"/>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1">
         <v>38</v>
       </c>
@@ -1011,9 +1105,11 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1">
         <v>39</v>
       </c>
@@ -1023,9 +1119,11 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1">
         <v>40</v>
       </c>
@@ -1035,9 +1133,11 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1">
         <v>41</v>
       </c>
@@ -1047,9 +1147,11 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1">
         <v>42</v>
       </c>
@@ -1059,9 +1161,11 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1">
         <v>43</v>
       </c>
@@ -1071,9 +1175,11 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="4"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1">
         <v>44</v>
       </c>
@@ -1083,9 +1189,11 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1">
         <v>45</v>
       </c>
@@ -1095,9 +1203,11 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1">
         <v>46</v>
       </c>
@@ -1107,9 +1217,11 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1">
         <v>47</v>
       </c>
@@ -1119,9 +1231,11 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1">
         <v>48</v>
       </c>
@@ -1131,9 +1245,11 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1">
         <v>49</v>
       </c>
@@ -1143,9 +1259,11 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="5"/>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1">
         <v>50</v>
       </c>
@@ -1155,9 +1273,11 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="1">
         <v>51</v>
       </c>
@@ -1167,9 +1287,11 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="1">
         <v>52</v>
       </c>
@@ -1179,9 +1301,11 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="5"/>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="1">
         <v>53</v>
       </c>
@@ -1191,9 +1315,11 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="5"/>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="1">
         <v>54</v>
       </c>
@@ -1203,9 +1329,11 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="5"/>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="1">
         <v>55</v>
       </c>
@@ -1215,9 +1343,11 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="5"/>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="1">
         <v>56</v>
       </c>
@@ -1227,9 +1357,11 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="4"/>
-      <c r="H59" s="5"/>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="1">
         <v>57</v>
       </c>
@@ -1239,9 +1371,11 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="4"/>
-      <c r="H60" s="5"/>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="1">
         <v>58</v>
       </c>
@@ -1251,9 +1385,11 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="4"/>
-      <c r="H61" s="5"/>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="1">
         <v>59</v>
       </c>
@@ -1263,9 +1399,11 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="4"/>
-      <c r="H62" s="5"/>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="1">
         <v>60</v>
       </c>
@@ -1275,9 +1413,11 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="1">
         <v>61</v>
       </c>
@@ -1287,9 +1427,11 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="5"/>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="1">
         <v>62</v>
       </c>
@@ -1299,9 +1441,11 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="5"/>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="5"/>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="1">
         <v>63</v>
       </c>
@@ -1311,9 +1455,11 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="5"/>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="5"/>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="1">
         <v>64</v>
       </c>
@@ -1323,9 +1469,11 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="5"/>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="5"/>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="1">
         <v>65</v>
       </c>
@@ -1335,9 +1483,11 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="4"/>
-      <c r="H68" s="5"/>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="5"/>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="1">
         <v>66</v>
       </c>
@@ -1347,9 +1497,11 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="4"/>
-      <c r="H69" s="5"/>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="5"/>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="1">
         <v>67</v>
       </c>
@@ -1359,9 +1511,11 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="4"/>
-      <c r="H70" s="5"/>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="5"/>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="1">
         <v>68</v>
       </c>
@@ -1371,9 +1525,11 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="4"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>69</v>
       </c>
@@ -1383,9 +1539,11 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="4"/>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="1">
         <v>70</v>
       </c>
@@ -1395,9 +1553,11 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="4"/>
-      <c r="H73" s="5"/>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="1">
         <v>71</v>
       </c>
@@ -1407,9 +1567,11 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>72</v>
       </c>
@@ -1419,9 +1581,11 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="1">
         <v>73</v>
       </c>
@@ -1431,9 +1595,11 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="4"/>
-      <c r="H76" s="5"/>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="1">
         <v>74</v>
       </c>
@@ -1443,9 +1609,11 @@
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="4"/>
-      <c r="H77" s="5"/>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>75</v>
       </c>
@@ -1455,9 +1623,11 @@
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="5"/>
-    </row>
-    <row r="79" spans="1:8">
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="1">
         <v>76</v>
       </c>
@@ -1467,9 +1637,11 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="4"/>
-      <c r="H79" s="5"/>
-    </row>
-    <row r="80" spans="1:8">
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="1">
         <v>77</v>
       </c>
@@ -1479,9 +1651,11 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="4"/>
-      <c r="H80" s="5"/>
-    </row>
-    <row r="81" spans="1:8">
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="1">
         <v>78</v>
       </c>
@@ -1491,9 +1665,11 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="4"/>
-      <c r="H81" s="5"/>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="1">
         <v>79</v>
       </c>
@@ -1503,9 +1679,11 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="4"/>
-      <c r="H82" s="5"/>
-    </row>
-    <row r="83" spans="1:8">
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="1">
         <v>80</v>
       </c>
@@ -1515,9 +1693,11 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="4"/>
-      <c r="H83" s="5"/>
-    </row>
-    <row r="84" spans="1:8">
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="1">
         <v>81</v>
       </c>
@@ -1527,9 +1707,11 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="4"/>
-      <c r="H84" s="5"/>
-    </row>
-    <row r="85" spans="1:8">
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="1">
         <v>82</v>
       </c>
@@ -1539,9 +1721,11 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="4"/>
-      <c r="H85" s="5"/>
-    </row>
-    <row r="86" spans="1:8">
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="1">
         <v>83</v>
       </c>
@@ -1551,9 +1735,11 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="4"/>
-      <c r="H86" s="5"/>
-    </row>
-    <row r="87" spans="1:8">
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="1">
         <v>84</v>
       </c>
@@ -1563,9 +1749,11 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="4"/>
-      <c r="H87" s="5"/>
-    </row>
-    <row r="88" spans="1:8">
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="1">
         <v>85</v>
       </c>
@@ -1575,9 +1763,11 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="4"/>
-      <c r="H88" s="5"/>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="1">
         <v>86</v>
       </c>
@@ -1587,9 +1777,11 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="4"/>
-      <c r="H89" s="5"/>
-    </row>
-    <row r="90" spans="1:8">
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="1">
         <v>87</v>
       </c>
@@ -1599,9 +1791,11 @@
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="4"/>
-      <c r="H90" s="5"/>
-    </row>
-    <row r="91" spans="1:8">
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="1">
         <v>88</v>
       </c>
@@ -1611,9 +1805,11 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="4"/>
-      <c r="H91" s="5"/>
-    </row>
-    <row r="92" spans="1:8">
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="1">
         <v>89</v>
       </c>
@@ -1623,9 +1819,11 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="4"/>
-      <c r="H92" s="5"/>
-    </row>
-    <row r="93" spans="1:8">
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="1">
         <v>90</v>
       </c>
@@ -1635,9 +1833,11 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="4"/>
-      <c r="H93" s="5"/>
-    </row>
-    <row r="94" spans="1:8">
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="1">
         <v>91</v>
       </c>
@@ -1647,9 +1847,11 @@
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="5"/>
-    </row>
-    <row r="95" spans="1:8">
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="1">
         <v>92</v>
       </c>
@@ -1659,9 +1861,11 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="4"/>
-      <c r="H95" s="5"/>
-    </row>
-    <row r="96" spans="1:8">
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="1">
         <v>93</v>
       </c>
@@ -1671,9 +1875,11 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="5"/>
-    </row>
-    <row r="97" spans="1:8">
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" s="1">
         <v>94</v>
       </c>
@@ -1683,9 +1889,11 @@
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="5"/>
-    </row>
-    <row r="98" spans="1:8">
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" s="1">
         <v>95</v>
       </c>
@@ -1695,9 +1903,11 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="5"/>
-    </row>
-    <row r="99" spans="1:8">
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" s="1">
         <v>96</v>
       </c>
@@ -1707,9 +1917,11 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="5"/>
-    </row>
-    <row r="100" spans="1:8">
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="1">
         <v>97</v>
       </c>
@@ -1719,9 +1931,11 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="4"/>
-      <c r="H100" s="5"/>
-    </row>
-    <row r="101" spans="1:8">
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="1">
         <v>98</v>
       </c>
@@ -1731,9 +1945,11 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="5"/>
-    </row>
-    <row r="102" spans="1:8">
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="1">
         <v>99</v>
       </c>
@@ -1743,9 +1959,11 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="4"/>
-      <c r="H102" s="5"/>
-    </row>
-    <row r="103" spans="1:8">
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="5"/>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="1">
         <v>100</v>
       </c>
@@ -1755,7 +1973,9 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="4"/>
-      <c r="H103" s="5"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/nongup_josagu/nongup_area_josagu.xlsx
+++ b/nongup_josagu/nongup_area_josagu.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>완료회차</t>
+          <t>담당자ID</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,11 @@
           <t>0011</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="F4" s="3" t="n"/>
